--- a/Team-Data/2013-14/1-22-2013-14.xlsx
+++ b/Team-Data/2013-14/1-22-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.537</v>
+        <v>0.525</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -682,10 +749,10 @@
         <v>82.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M2" t="n">
         <v>25.5</v>
@@ -694,22 +761,22 @@
         <v>0.367</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P2" t="n">
         <v>21.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>31.8</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
         <v>25.6</v>
@@ -718,46 +785,46 @@
         <v>15.2</v>
       </c>
       <c r="W2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="AC2" t="n">
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -769,7 +836,7 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
@@ -793,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.341</v>
+        <v>0.326</v>
       </c>
       <c r="H3" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K3" t="n">
         <v>0.438</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.332</v>
+        <v>0.328</v>
       </c>
       <c r="O3" t="n">
         <v>16.1</v>
@@ -882,13 +949,13 @@
         <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
         <v>42.8</v>
@@ -897,13 +964,13 @@
         <v>19.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W3" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
@@ -912,19 +979,19 @@
         <v>21.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
@@ -933,10 +1000,10 @@
         <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>14</v>
@@ -963,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
@@ -978,19 +1045,19 @@
         <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1130,7 +1197,7 @@
         <v>14</v>
       </c>
       <c r="AM4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN4" t="n">
         <v>8</v>
@@ -1145,7 +1212,7 @@
         <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>23</v>
@@ -1157,16 +1224,16 @@
         <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
         <v>23</v>
@@ -1178,7 +1245,7 @@
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.432</v>
+        <v>0.419</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,10 +1292,10 @@
         <v>35</v>
       </c>
       <c r="J5" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L5" t="n">
         <v>5.5</v>
@@ -1240,16 +1307,16 @@
         <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.729</v>
+        <v>0.731</v>
       </c>
       <c r="R5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S5" t="n">
         <v>32.6</v>
@@ -1258,7 +1325,7 @@
         <v>41.8</v>
       </c>
       <c r="U5" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
         <v>12.8</v>
@@ -1267,7 +1334,7 @@
         <v>6.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.7</v>
@@ -1282,7 +1349,7 @@
         <v>94</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1291,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1303,7 +1370,7 @@
         <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,16 +1382,16 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
         <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
         <v>23</v>
@@ -1360,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.512</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>49</v>
@@ -1407,31 +1474,31 @@
         <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.427</v>
+        <v>0.425</v>
       </c>
       <c r="L6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.339</v>
+        <v>0.334</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0.769</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S6" t="n">
         <v>33.1</v>
@@ -1443,7 +1510,7 @@
         <v>22.3</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W6" t="n">
         <v>7.1</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1485,10 +1552,10 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1497,25 +1564,25 @@
         <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>12</v>
@@ -1524,10 +1591,10 @@
         <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="n">
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.357</v>
+        <v>0.366</v>
       </c>
       <c r="H7" t="n">
         <v>49</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J7" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.425</v>
+        <v>0.427</v>
       </c>
       <c r="L7" t="n">
         <v>7.2</v>
@@ -1601,37 +1668,37 @@
         <v>19.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O7" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R7" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S7" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T7" t="n">
         <v>44.5</v>
       </c>
       <c r="U7" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V7" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" t="n">
         <v>6</v>
@@ -1640,22 +1707,22 @@
         <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
         <v>24</v>
@@ -1664,19 +1731,19 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN7" t="n">
         <v>13</v>
@@ -1685,13 +1752,13 @@
         <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
         <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
         <v>15</v>
@@ -1703,10 +1770,10 @@
         <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1715,10 +1782,10 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -1753,67 +1820,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.377</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.793</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
         <v>9.6</v>
       </c>
       <c r="S8" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T8" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="U8" t="n">
         <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="X8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1825,10 +1892,10 @@
         <v>18.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.5</v>
+        <v>104</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1840,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>28</v>
@@ -1855,7 +1922,7 @@
         <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
         <v>10</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1873,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>26</v>
@@ -1882,10 +1949,10 @@
         <v>29</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,13 +1964,13 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -2013,28 +2080,28 @@
         <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
         <v>10</v>
@@ -2043,16 +2110,16 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2070,10 +2137,10 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2184,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>0.405</v>
+        <v>0.415</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J10" t="n">
         <v>85.59999999999999</v>
@@ -2144,58 +2211,58 @@
         <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.306</v>
+        <v>0.307</v>
       </c>
       <c r="O10" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.664</v>
+        <v>0.662</v>
       </c>
       <c r="R10" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
         <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U10" t="n">
         <v>20.4</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W10" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y10" t="n">
         <v>4.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2213,7 +2280,7 @@
         <v>11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK10" t="n">
         <v>18</v>
@@ -2222,7 +2289,7 @@
         <v>27</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2249,19 +2316,19 @@
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2410,10 +2477,10 @@
         <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
@@ -2422,7 +2489,7 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
@@ -2437,19 +2504,19 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA11" t="n">
         <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.659</v>
+        <v>0.651</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J12" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K12" t="n">
         <v>0.473</v>
@@ -2508,34 +2575,34 @@
         <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
         <v>21.9</v>
       </c>
       <c r="P12" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="U12" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
         <v>7.4</v>
@@ -2550,31 +2617,31 @@
         <v>20.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.9</v>
+        <v>105.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2586,7 +2653,7 @@
         <v>6</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
         <v>24</v>
@@ -2604,13 +2671,13 @@
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
@@ -2625,13 +2692,13 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.805</v>
+        <v>0.825</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="K13" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N13" t="n">
         <v>0.364</v>
@@ -2699,37 +2766,37 @@
         <v>17.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.788</v>
+        <v>0.791</v>
       </c>
       <c r="R13" t="n">
         <v>9.9</v>
       </c>
       <c r="S13" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="T13" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W13" t="n">
         <v>7.2</v>
       </c>
       <c r="X13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA13" t="n">
         <v>21.7</v>
@@ -2738,10 +2805,10 @@
         <v>98.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2762,16 +2829,16 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2786,28 +2853,28 @@
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
         <v>29</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.659</v>
+        <v>0.674</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,10 +2930,10 @@
         <v>38.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L14" t="n">
         <v>8.1</v>
@@ -2875,13 +2942,13 @@
         <v>24.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.73</v>
@@ -2908,19 +2975,19 @@
         <v>4.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z14" t="n">
         <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.4</v>
+        <v>105.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2935,10 +3002,10 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2947,22 +3014,22 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2971,7 +3038,7 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>15</v>
@@ -2995,10 +3062,10 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC14" t="n">
         <v>5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>21</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
         <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>19</v>
@@ -3141,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>10</v>
@@ -3168,10 +3235,10 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3354,25 @@
         <v>-0.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF16" t="n">
         <v>12</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK16" t="n">
         <v>13</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3362,7 +3429,7 @@
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3493,22 +3560,22 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN17" t="n">
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3529,13 +3596,13 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
         <v>11</v>
@@ -3544,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="H18" t="n">
         <v>48.9</v>
       </c>
       <c r="I18" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J18" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.422</v>
+        <v>0.42</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O18" t="n">
         <v>14.8</v>
@@ -3612,7 +3679,7 @@
         <v>19.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="R18" t="n">
         <v>11.3</v>
@@ -3621,37 +3688,37 @@
         <v>30.1</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X18" t="n">
         <v>5.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z18" t="n">
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3675,40 +3742,40 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP18" t="n">
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
         <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -3833,22 +3900,22 @@
         <v>5</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3857,7 +3924,7 @@
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM19" t="n">
         <v>12</v>
@@ -3866,7 +3933,7 @@
         <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>21</v>
@@ -4036,7 +4103,7 @@
         <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>26</v>
@@ -4069,7 +4136,7 @@
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>10</v>
@@ -4090,7 +4157,7 @@
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.357</v>
+        <v>0.366</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4143,25 +4210,25 @@
         <v>0.433</v>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.356</v>
+        <v>0.352</v>
       </c>
       <c r="O21" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>29.6</v>
@@ -4170,7 +4237,7 @@
         <v>40.3</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V21" t="n">
         <v>12.9</v>
@@ -4179,7 +4246,7 @@
         <v>8</v>
       </c>
       <c r="X21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
         <v>3.8</v>
@@ -4188,28 +4255,28 @@
         <v>22.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>-4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>24</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4221,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM21" t="n">
         <v>8</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4236,7 +4303,7 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,7 +4315,7 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
@@ -4257,16 +4324,16 @@
         <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
         <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -4301,58 +4368,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.767</v>
+        <v>0.762</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="J22" t="n">
         <v>83</v>
       </c>
       <c r="K22" t="n">
-        <v>0.468</v>
+        <v>0.466</v>
       </c>
       <c r="L22" t="n">
         <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="P22" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R22" t="n">
         <v>11.3</v>
       </c>
       <c r="S22" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="T22" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V22" t="n">
         <v>15.6</v>
@@ -4367,34 +4434,34 @@
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.5</v>
+        <v>105.3</v>
       </c>
       <c r="AC22" t="n">
         <v>7.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
         <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>15</v>
@@ -4409,25 +4476,25 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
       </c>
       <c r="AP22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>16</v>
@@ -4445,13 +4512,13 @@
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>0.256</v>
+        <v>0.262</v>
       </c>
       <c r="H23" t="n">
         <v>48.8</v>
       </c>
       <c r="I23" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="n">
         <v>7.2</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O23" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P23" t="n">
         <v>21.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
         <v>20.5</v>
@@ -4543,7 +4610,7 @@
         <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
@@ -4552,16 +4619,16 @@
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.9</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,49 +4640,49 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
       </c>
       <c r="AJ23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK23" t="n">
         <v>21</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>18</v>
       </c>
       <c r="AM23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN23" t="n">
         <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
         <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,13 +4691,13 @@
         <v>27</v>
       </c>
       <c r="AY23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.333</v>
+        <v>0.317</v>
       </c>
       <c r="H24" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I24" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J24" t="n">
         <v>88.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L24" t="n">
         <v>6.9</v>
       </c>
       <c r="M24" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="O24" t="n">
         <v>16.3</v>
       </c>
       <c r="P24" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
         <v>0.707</v>
       </c>
       <c r="R24" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T24" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="U24" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="W24" t="n">
         <v>8.9</v>
@@ -4728,34 +4795,34 @@
         <v>4.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA24" t="n">
         <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>101.4</v>
+        <v>101.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
         <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="n">
         <v>4</v>
@@ -4764,13 +4831,13 @@
         <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN24" t="n">
         <v>29</v>
@@ -4785,16 +4852,16 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4812,7 +4879,7 @@
         <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -4847,67 +4914,67 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>17</v>
       </c>
       <c r="G25" t="n">
-        <v>0.585</v>
+        <v>0.575</v>
       </c>
       <c r="H25" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.456</v>
+        <v>0.453</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="N25" t="n">
-        <v>0.367</v>
+        <v>0.362</v>
       </c>
       <c r="O25" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R25" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V25" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
         <v>8.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y25" t="n">
         <v>4.2</v>
@@ -4916,16 +4983,16 @@
         <v>21.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.4</v>
+        <v>103.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,43 +5001,43 @@
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
         <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
         <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
         <v>12</v>
@@ -4985,7 +5052,7 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -4994,10 +5061,10 @@
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5119,7 +5186,7 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5155,13 +5222,13 @@
         <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="n">
         <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J27" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="M27" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O27" t="n">
         <v>19.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.766</v>
+        <v>0.771</v>
       </c>
       <c r="R27" t="n">
         <v>11.8</v>
@@ -5259,13 +5326,13 @@
         <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U27" t="n">
         <v>20.1</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
         <v>7.7</v>
@@ -5274,7 +5341,7 @@
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z27" t="n">
         <v>22.7</v>
@@ -5283,76 +5350,76 @@
         <v>22.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
         <v>23</v>
       </c>
       <c r="AH27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI27" t="n">
         <v>15</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>16</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
         <v>13</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -5393,55 +5460,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
         <v>32</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.762</v>
+        <v>0.78</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="J28" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.494</v>
+        <v>0.493</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.405</v>
+        <v>0.403</v>
       </c>
       <c r="O28" t="n">
         <v>14.8</v>
       </c>
       <c r="P28" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
         <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="T28" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="U28" t="n">
         <v>25.2</v>
@@ -5453,7 +5520,7 @@
         <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5462,25 +5529,25 @@
         <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB28" t="n">
         <v>104.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
         <v>26</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
@@ -5516,25 +5583,25 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.512</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L29" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>22.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O29" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P29" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.768</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
         <v>12</v>
@@ -5623,37 +5690,37 @@
         <v>31.3</v>
       </c>
       <c r="T29" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U29" t="n">
         <v>20.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5665,13 +5732,13 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
@@ -5683,10 +5750,10 @@
         <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
@@ -5704,16 +5771,16 @@
         <v>14</v>
       </c>
       <c r="AU29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5725,7 +5792,7 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>-6.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF30" t="n">
         <v>27</v>
       </c>
       <c r="AG30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>24</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
         <v>26</v>
@@ -5874,7 +5941,7 @@
         <v>25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>18</v>
@@ -5883,16 +5950,16 @@
         <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0.488</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J31" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.449</v>
@@ -5969,70 +6036,70 @@
         <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="O31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0.73</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T31" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U31" t="n">
         <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
         <v>8.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="AC31" t="n">
         <v>-0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI31" t="n">
         <v>16</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>15</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6056,43 +6123,43 @@
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-22-2013-14</t>
+          <t>2014-01-22</t>
         </is>
       </c>
     </row>
